--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/设备信息表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/设备信息表.xlsx
@@ -519,8 +519,14 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800 V200R019C10SPC800</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>GA</t>
@@ -549,7 +555,11 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -587,8 +597,14 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800 V300R023C11</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>GA</t>
@@ -617,7 +633,11 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -655,7 +675,9 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>64</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -665,7 +687,11 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -703,7 +729,9 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>76</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -713,7 +741,11 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -751,8 +783,14 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>585</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD 1.0.T33</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>GA</t>
@@ -781,7 +819,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1719,14 +1761,8 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>64</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CloudEngine 16800 V300</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>GA</t>
@@ -1755,11 +1791,7 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1797,14 +1829,8 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>76</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CloudEngine 9800 V200R025C00</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>GA</t>
@@ -1833,11 +1859,7 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1875,9 +1897,7 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>64</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1887,11 +1907,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1929,9 +1945,7 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>76</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1941,11 +1955,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1983,14 +1993,8 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>585</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Atlas 900 A3 SuperPoD 1.0.T25</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2019,11 +2023,7 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
